--- a/sheets/조재수대금교본/검수/참새와 허수아비.xlsx
+++ b/sheets/조재수대금교본/검수/참새와 허수아비.xlsx
@@ -5141,7 +5141,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -5230,11 +5230,7 @@
     </row>
     <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B5" s="21"/>
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
@@ -5289,7 +5285,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="C6" s="22"/>
@@ -5391,24 +5387,16 @@
     </row>
     <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢ㄴ</t>
+潢</t>
         </is>
       </c>
       <c r="E8" s="24"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
@@ -5419,22 +5407,19 @@
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃ㄴ
-‹</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="O8" s="24"/>
@@ -5636,47 +5621,19 @@
     </row>
     <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B14" s="21"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
       <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
@@ -5725,7 +5682,7 @@
       <c r="G17" s="22"/>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="I17" s="22"/>
@@ -5737,7 +5694,7 @@
       <c r="K17" s="22"/>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="M17" s="22"/>
@@ -5844,8 +5801,7 @@
       <c r="Q19" s="24"/>
       <c r="R19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="S19" s="24"/>
@@ -5877,7 +5833,7 @@
       <c r="K20" s="22"/>
       <c r="L20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢ㄴ
+          <t xml:space="preserve">潢潢
 –</t>
         </is>
       </c>
@@ -5927,8 +5883,7 @@
       <c r="Q21" s="23"/>
       <c r="R21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕
-‹</t>
+          <t xml:space="preserve">潕</t>
         </is>
       </c>
       <c r="S21" s="23"/>
@@ -5941,43 +5896,31 @@
       <c r="E22" s="24"/>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ㄴ
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G22" s="24"/>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H22" s="21"/>
       <c r="I22" s="24"/>
       <c r="J22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="K22" s="24"/>
       <c r="L22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="M22" s="24"/>
       <c r="N22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="O22" s="24"/>
-      <c r="P22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P22" s="21"/>
       <c r="Q22" s="24"/>
       <c r="R22" s="21" t="inlineStr">
         <is>
@@ -6001,7 +5944,7 @@
       <c r="G23" s="22"/>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ㄴ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I23" s="22"/>
@@ -6174,41 +6117,17 @@
         </is>
       </c>
       <c r="G28" s="24"/>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H28" s="21"/>
       <c r="I28" s="24"/>
-      <c r="J28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J28" s="21"/>
       <c r="K28" s="24"/>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L28" s="21"/>
       <c r="M28" s="24"/>
-      <c r="N28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N28" s="21"/>
       <c r="O28" s="24"/>
-      <c r="P28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P28" s="21"/>
       <c r="Q28" s="24"/>
-      <c r="R28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R28" s="21"/>
       <c r="S28" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/참새와 허수아비.xlsx
+++ b/sheets/조재수대금교본/검수/참새와 허수아비.xlsx
@@ -5141,7 +5141,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -5285,7 +5285,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="C6" s="22"/>
@@ -5392,7 +5392,7 @@
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
+潢ㄴ</t>
         </is>
       </c>
       <c r="E8" s="24"/>
@@ -5413,7 +5413,7 @@
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
+          <t xml:space="preserve">黃ㄴ</t>
         </is>
       </c>
       <c r="M8" s="24"/>
@@ -5682,7 +5682,7 @@
       <c r="G17" s="22"/>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="I17" s="22"/>
@@ -5694,7 +5694,7 @@
       <c r="K17" s="22"/>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="M17" s="22"/>
@@ -5833,7 +5833,7 @@
       <c r="K20" s="22"/>
       <c r="L20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢
+          <t xml:space="preserve">潢潢ㄴ
 –</t>
         </is>
       </c>
@@ -5896,7 +5896,7 @@
       <c r="E22" s="24"/>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ㄴ</t>
         </is>
       </c>
       <c r="G22" s="24"/>
@@ -5944,7 +5944,7 @@
       <c r="G23" s="22"/>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ㄴ</t>
         </is>
       </c>
       <c r="I23" s="22"/>

--- a/sheets/조재수대금교본/검수/참새와 허수아비.xlsx
+++ b/sheets/조재수대금교본/검수/참새와 허수아비.xlsx
@@ -5089,30 +5089,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="15.29" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="64.52" customHeight="true">
+    <row r="2" ht="90.91" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="96.05" customHeight="true">
+    <row r="3" ht="135.55" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="96.05" customHeight="true">
+    <row r="4" ht="135.55" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -5228,7 +5228,7 @@
       <c r="R4" s="21"/>
       <c r="S4" s="23"/>
     </row>
-    <row r="5" ht="96.05" customHeight="true">
+    <row r="5" ht="135.55" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="S5" s="24"/>
     </row>
-    <row r="6" ht="96.05" customHeight="true">
+    <row r="6" ht="135.55" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="96.05" customHeight="true">
+    <row r="7" ht="135.55" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -5385,7 +5385,7 @@
       <c r="R7" s="21"/>
       <c r="S7" s="23"/>
     </row>
-    <row r="8" ht="96.05" customHeight="true">
+    <row r="8" ht="135.55" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="S8" s="24"/>
     </row>
-    <row r="9" ht="96.05" customHeight="true">
+    <row r="9" ht="135.55" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="96.05" customHeight="true">
+    <row r="10" ht="135.55" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -5516,7 +5516,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="23"/>
     </row>
-    <row r="11" ht="96.05" customHeight="true">
+    <row r="11" ht="135.55" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="S11" s="24"/>
     </row>
-    <row r="12" ht="96.05" customHeight="true">
+    <row r="12" ht="135.55" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="96.05" customHeight="true">
+    <row r="13" ht="135.55" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -5619,7 +5619,7 @@
       <c r="R13" s="21"/>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" ht="96.05" customHeight="true">
+    <row r="14" ht="135.55" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -5643,7 +5643,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="64.52" customHeight="true">
+    <row r="16" ht="90.91" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
       <c r="R16" s="20"/>
       <c r="S16" s="20"/>
     </row>
-    <row r="17" ht="96.05" customHeight="true">
+    <row r="17" ht="135.55" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="S17" s="22"/>
     </row>
-    <row r="18" ht="96.05" customHeight="true">
+    <row r="18" ht="135.55" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -5757,7 +5757,7 @@
       <c r="R18" s="21"/>
       <c r="S18" s="23"/>
     </row>
-    <row r="19" ht="96.05" customHeight="true">
+    <row r="19" ht="135.55" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="S19" s="24"/>
     </row>
-    <row r="20" ht="96.05" customHeight="true">
+    <row r="20" ht="135.55" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="S20" s="22"/>
     </row>
-    <row r="21" ht="96.05" customHeight="true">
+    <row r="21" ht="135.55" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="S21" s="23"/>
     </row>
-    <row r="22" ht="96.05" customHeight="true">
+    <row r="22" ht="135.55" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="S22" s="24"/>
     </row>
-    <row r="23" ht="96.05" customHeight="true">
+    <row r="23" ht="135.55" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="S23" s="22"/>
     </row>
-    <row r="24" ht="96.05" customHeight="true">
+    <row r="24" ht="135.55" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -6009,7 +6009,7 @@
       <c r="R24" s="21"/>
       <c r="S24" s="23"/>
     </row>
-    <row r="25" ht="96.05" customHeight="true">
+    <row r="25" ht="135.55" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -6047,7 +6047,7 @@
       <c r="R25" s="21"/>
       <c r="S25" s="24"/>
     </row>
-    <row r="26" ht="96.05" customHeight="true">
+    <row r="26" ht="135.55" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -6084,7 +6084,7 @@
       <c r="R26" s="21"/>
       <c r="S26" s="22"/>
     </row>
-    <row r="27" ht="96.05" customHeight="true">
+    <row r="27" ht="135.55" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -6105,7 +6105,7 @@
       <c r="R27" s="21"/>
       <c r="S27" s="23"/>
     </row>
-    <row r="28" ht="96.05" customHeight="true">
+    <row r="28" ht="135.55" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -6137,7 +6137,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="44"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
